--- a/信息工程系人名单网页版.xlsx
+++ b/信息工程系人名单网页版.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
   <si>
     <t>序号</t>
   </si>
@@ -35,6 +35,9 @@
     <t>姓名</t>
   </si>
   <si>
+    <t>教师类别</t>
+  </si>
+  <si>
     <t>杨赛</t>
   </si>
   <si>
@@ -89,6 +92,27 @@
     <t>李淑娟</t>
   </si>
   <si>
+    <t>朱连华</t>
+  </si>
+  <si>
+    <t>包玉文</t>
+  </si>
+  <si>
+    <t>吴超</t>
+  </si>
+  <si>
+    <t>王春艳</t>
+  </si>
+  <si>
+    <t>高汉春</t>
+  </si>
+  <si>
+    <t>贾红霞</t>
+  </si>
+  <si>
+    <t>杨占新</t>
+  </si>
+  <si>
     <t>吴亚斌</t>
   </si>
   <si>
@@ -98,9 +122,6 @@
     <t>外聘</t>
   </si>
   <si>
-    <t>李佳展</t>
-  </si>
-  <si>
     <t>李连花</t>
   </si>
   <si>
@@ -131,19 +152,49 @@
     <t>石洁</t>
   </si>
   <si>
+    <t>孟思</t>
+  </si>
+  <si>
+    <t>刘旭</t>
+  </si>
+  <si>
+    <t>牛旭</t>
+  </si>
+  <si>
+    <t>王光才</t>
+  </si>
+  <si>
+    <t>谭姝</t>
+  </si>
+  <si>
+    <t>葛俞珊</t>
+  </si>
+  <si>
+    <t>李祎萌</t>
+  </si>
+  <si>
+    <t>肖一萌</t>
+  </si>
+  <si>
     <t>谢燕红</t>
   </si>
   <si>
-    <t>外聘（见习岗）</t>
-  </si>
-  <si>
-    <t>高思航</t>
+    <t>见习岗</t>
+  </si>
+  <si>
+    <t>吴景琦</t>
+  </si>
+  <si>
+    <t>刘芳羽</t>
+  </si>
+  <si>
+    <t>陈思文</t>
   </si>
   <si>
     <t>赵君杰</t>
   </si>
   <si>
-    <t>临聘</t>
+    <t>50元临聘</t>
   </si>
   <si>
     <t>贾霖霖</t>
@@ -326,7 +377,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,36 +386,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -550,39 +571,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -594,7 +587,7 @@
         <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -725,7 +718,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -737,119 +730,119 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -862,29 +855,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1411,524 +1383,910 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="4"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13.6666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.4444444444444" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
-      <c r="A2" s="6">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="D2" s="7">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:5">
-      <c r="A3" s="6">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:8">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:8">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="4">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:8">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4">
+        <v>11</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:8">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4">
+        <v>12</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:8">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4">
+        <v>13</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:8">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="4">
+        <v>14</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4">
+        <v>17</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="4">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4">
+        <v>19</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="4">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4">
+        <v>4</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4">
+        <v>5</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4">
+        <v>6</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4">
+        <v>7</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4">
+        <v>8</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4">
+        <v>9</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4">
+        <v>11</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4">
+        <v>12</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4">
+        <v>13</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4">
+        <v>14</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4">
+        <v>15</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4">
+        <v>16</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4">
+        <v>17</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4">
+        <v>18</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4">
+        <v>19</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:5">
-      <c r="A4" s="6">
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="7">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:5">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="7">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:5">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8">
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4">
+        <v>4</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:5">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7">
-        <v>5</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:5">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="7">
-        <v>6</v>
-      </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:5">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>7</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:5">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:5">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="7">
-        <v>9</v>
-      </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:5">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7">
-        <v>10</v>
-      </c>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:5">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="7">
-        <v>11</v>
-      </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:5">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="7">
-        <v>12</v>
-      </c>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:5">
-      <c r="A15" s="6">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="7">
-        <v>13</v>
-      </c>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:5">
-      <c r="A16" s="6">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="7">
-        <v>14</v>
-      </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:5">
-      <c r="A17" s="6">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="7">
-        <v>15</v>
-      </c>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:5">
-      <c r="A18" s="6">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="9">
-        <v>1</v>
-      </c>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2</v>
-      </c>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="9">
-        <v>3</v>
-      </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="9">
-        <v>4</v>
-      </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6">
-        <v>22</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="9">
-        <v>5</v>
-      </c>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6">
-        <v>23</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="9">
-        <v>6</v>
-      </c>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6">
-        <v>24</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="9">
-        <v>7</v>
-      </c>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6">
-        <v>25</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="9">
-        <v>8</v>
-      </c>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="9">
-        <v>9</v>
-      </c>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6">
-        <v>27</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="9">
-        <v>10</v>
-      </c>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6">
-        <v>28</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="9">
-        <v>11</v>
-      </c>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6">
-        <v>29</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="9">
-        <v>12</v>
-      </c>
-      <c r="E30" s="9"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="9">
-        <v>13</v>
-      </c>
-      <c r="E31" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6">
-        <v>31</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="9">
-        <v>14</v>
-      </c>
-      <c r="E32" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6">
-        <v>32</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6">
-        <v>33</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="11">
+    <row r="50" spans="1:8">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4">
         <v>2</v>
       </c>
     </row>

--- a/信息工程系人名单网页版.xlsx
+++ b/信息工程系人名单网页版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="24000" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
   <si>
     <t>序号</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>陈思文</t>
+  </si>
+  <si>
+    <t>关天昊</t>
   </si>
   <si>
     <t>赵君杰</t>
@@ -1383,7 +1386,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2262,31 +2265,49 @@
         <v>54</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4">
-        <v>1</v>
-      </c>
+      <c r="G49" s="4">
+        <v>5</v>
+      </c>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4">
         <v>2</v>
       </c>
     </row>

--- a/信息工程系人名单网页版.xlsx
+++ b/信息工程系人名单网页版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9720"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
   <si>
     <t>序号</t>
   </si>
@@ -134,9 +134,6 @@
     <t>陈颖超</t>
   </si>
   <si>
-    <t>符恺璐</t>
-  </si>
-  <si>
     <t>孟久轩</t>
   </si>
   <si>
@@ -194,10 +191,16 @@
     <t>关天昊</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>赵君杰</t>
   </si>
   <si>
     <t>50元临聘</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>贾霖霖</t>
@@ -1386,7 +1389,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1946,7 +1949,7 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1964,7 +1967,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1982,7 +1985,7 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -2000,7 +2003,7 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -2018,7 +2021,7 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -2036,7 +2039,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -2054,7 +2057,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2072,7 +2075,7 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2090,7 +2093,7 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2108,7 +2111,7 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -2126,7 +2129,7 @@
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -2144,7 +2147,7 @@
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -2162,7 +2165,7 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -2175,14 +2178,14 @@
         <v>48</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="4">
-        <v>19</v>
-      </c>
-      <c r="G44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4">
+        <v>1</v>
+      </c>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8">
@@ -2190,16 +2193,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="4"/>
     </row>
@@ -2211,13 +2214,13 @@
         <v>51</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="4"/>
     </row>
@@ -2229,13 +2232,13 @@
         <v>52</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="4"/>
     </row>
@@ -2247,40 +2250,40 @@
         <v>53</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="3">
-        <v>48</v>
+      <c r="A49" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4">
-        <v>5</v>
-      </c>
-      <c r="H49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="3">
-        <v>49</v>
+      <c r="A50" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>56</v>
@@ -2290,24 +2293,6 @@
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="3">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4">
         <v>2</v>
       </c>
     </row>

--- a/信息工程系人名单网页版.xlsx
+++ b/信息工程系人名单网页版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="10308"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
   <si>
     <t>序号</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>关天昊</t>
+  </si>
+  <si>
+    <t>白小汇</t>
+  </si>
+  <si>
+    <t>李喆</t>
   </si>
   <si>
     <t>1</t>
@@ -1389,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2261,38 +2267,74 @@
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4">
-        <v>1</v>
-      </c>
+      <c r="G49" s="4">
+        <v>6</v>
+      </c>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="3" t="s">
-        <v>57</v>
+      <c r="A50" s="3">
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4">
+      <c r="G50" s="4">
+        <v>7</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4">
         <v>2</v>
       </c>
     </row>

--- a/信息工程系人名单网页版.xlsx
+++ b/信息工程系人名单网页版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10308"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1955,7 +1955,7 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1973,7 +1973,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1991,7 +1991,7 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -2009,7 +2009,7 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -2027,7 +2027,7 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -2045,7 +2045,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -2063,7 +2063,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2081,7 +2081,7 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2099,7 +2099,7 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2117,7 +2117,7 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -2135,7 +2135,7 @@
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -2153,7 +2153,7 @@
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -2171,7 +2171,7 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>

--- a/信息工程系人名单网页版.xlsx
+++ b/信息工程系人名单网页版.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\微云同步助手\281475128776228\githubpages\xinxipingtai.github.io\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="21600" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
   <si>
     <t>序号</t>
   </si>
@@ -98,6 +103,9 @@
     <t>包玉文</t>
   </si>
   <si>
+    <t>即将退休</t>
+  </si>
+  <si>
     <t>吴超</t>
   </si>
   <si>
@@ -137,6 +145,9 @@
     <t>孟久轩</t>
   </si>
   <si>
+    <t>生孩子</t>
+  </si>
+  <si>
     <t>王艳会</t>
   </si>
   <si>
@@ -176,25 +187,25 @@
     <t>谢燕红</t>
   </si>
   <si>
+    <t>吴景琦</t>
+  </si>
+  <si>
+    <t>刘芳羽</t>
+  </si>
+  <si>
+    <t>白小汇</t>
+  </si>
+  <si>
     <t>见习岗</t>
   </si>
   <si>
-    <t>吴景琦</t>
-  </si>
-  <si>
-    <t>刘芳羽</t>
-  </si>
-  <si>
-    <t>陈思文</t>
-  </si>
-  <si>
-    <t>关天昊</t>
-  </si>
-  <si>
-    <t>白小汇</t>
-  </si>
-  <si>
     <t>李喆</t>
+  </si>
+  <si>
+    <t>石羽彤</t>
+  </si>
+  <si>
+    <t>李焕荣</t>
   </si>
   <si>
     <t>1</t>
@@ -389,12 +400,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -730,7 +747,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -754,16 +771,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -772,90 +789,93 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -863,6 +883,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1395,946 +1424,954 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="7"/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.4444444444444" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="27.4444444444444" style="3" customWidth="1"/>
+    <col min="4" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="16.2962962962963" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="3">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
         <v>3</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="3">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5">
         <v>1</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="3">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
         <v>5</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="3">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5">
         <v>6</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="3">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
         <v>7</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="3">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
         <v>8</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="3">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
         <v>9</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="A12" s="3">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
         <v>10</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="A13" s="3">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
         <v>11</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="A14" s="3">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5">
         <v>12</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="A15" s="3">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
         <v>13</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="A16" s="3">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
         <v>14</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
-      <c r="A17" s="3">
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:9">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
         <v>15</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
-      <c r="A18" s="3">
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:9">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="5">
         <v>16</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="3">
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:9">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="C19" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="8">
         <v>17</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="3">
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="5">
+        <v>18</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="5">
+        <v>19</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>20</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="5">
+        <v>21</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="B24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="5">
+        <v>22</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5">
+        <v>2</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5">
+        <v>3</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5">
+        <v>4</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5">
+        <v>5</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5">
+        <v>6</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5">
+        <v>7</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="7">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5">
+        <v>8</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5">
+        <v>9</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5">
+        <v>10</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5">
+        <v>11</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5">
+        <v>12</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5">
+        <v>13</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5">
+        <v>14</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5">
+        <v>15</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5">
+        <v>16</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="6">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5">
+        <v>17</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="6">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5">
         <v>18</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="3">
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="6">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5">
+        <v>19</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="6">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="4">
-        <v>19</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="3">
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="6">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="4">
-        <v>20</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="4">
-        <v>21</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="4">
-        <v>22</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4">
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5">
         <v>2</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4">
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5">
+        <v>3</v>
+      </c>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5">
+        <v>4</v>
+      </c>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5">
         <v>1</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4">
-        <v>2</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4">
-        <v>3</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4">
-        <v>4</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4">
-        <v>5</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4">
-        <v>6</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="3">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4">
-        <v>7</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="3">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4">
-        <v>8</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="3">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4">
-        <v>9</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="3">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4">
-        <v>10</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="3">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4">
-        <v>11</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="3">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4">
-        <v>12</v>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="3">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4">
-        <v>13</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="3">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4">
-        <v>14</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="3">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4">
-        <v>15</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="3">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4">
-        <v>16</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="3">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4">
-        <v>17</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="3">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4">
-        <v>18</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="3">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4">
-        <v>1</v>
-      </c>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="3">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4">
-        <v>2</v>
-      </c>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="3">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4">
-        <v>3</v>
-      </c>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="3">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4">
-        <v>4</v>
-      </c>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="3">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4">
-        <v>5</v>
-      </c>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="3">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4">
-        <v>6</v>
-      </c>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="3">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4">
-        <v>7</v>
-      </c>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4">
-        <v>1</v>
-      </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="A52" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4">
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5">
         <v>2</v>
       </c>
     </row>
